--- a/output/pdf_financials_xlsx/EGM.xlsx
+++ b/output/pdf_financials_xlsx/EGM.xlsx
@@ -1328,7 +1328,7 @@
         <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2.659708</v>
+        <v>-0.70292</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1570,7 +1570,7 @@
         <v>-1.195704</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.681314</v>
+        <v>-1.681314</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-2.561966</v>
@@ -1744,7 +1744,7 @@
         <v>-1.195704</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.681314</v>
+        <v>-1.681314</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-2.561966</v>
@@ -2278,7 +2278,7 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-271.844267237943</v>
+        <v>-71.844267237943</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -5887,40 +5887,40 @@
         <v>11.854549</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>12.000449</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>12.109827</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>12.284496</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>12.310934</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>12.780694</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>13.391418</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>13.664525</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>13.838759</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>14.049721</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>14.049721</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>14.05261</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>14.05261</v>
       </c>
     </row>
     <row r="93">
@@ -7349,10 +7349,10 @@
         <v>0</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>-0.908802</v>
+        <v>-4.880872</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.390688</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
@@ -10314,7 +10314,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -11737,7 +11741,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -35114,7 +35122,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -52559,10 +52571,10 @@
         </is>
       </c>
       <c r="H447" s="5" t="n">
-        <v>1.681314</v>
+        <v>-1.681314</v>
       </c>
       <c r="I447" s="5" t="n">
-        <v>2.561966</v>
+        <v>-2.561966</v>
       </c>
       <c r="J447" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/EGM.xlsx
+++ b/output/pdf_financials_xlsx/EGM.xlsx
@@ -1029,25 +1029,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.211625</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.020953</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001812</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.011286</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.019456</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.001897</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.031524</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -2003,25 +2003,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.075086</v>
+        <v>-3.286711</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.753026</v>
+        <v>-1.773979</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.195704</v>
+        <v>-1.197516</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.978394</v>
+        <v>-0.98968</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.561966</v>
+        <v>-2.581422</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.161202</v>
+        <v>-1.163099</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.084618</v>
+        <v>0.053094</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.688768</v>
@@ -2119,25 +2119,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.075086</v>
+        <v>-3.286711</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.753026</v>
+        <v>-1.773979</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.195704</v>
+        <v>-1.197516</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.978394</v>
+        <v>-0.98968</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.486046</v>
+        <v>-2.505502</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.092497</v>
+        <v>-1.094394</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.133294</v>
+        <v>0.10177</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.654919</v>
@@ -2441,40 +2441,40 @@
         <v>0.638646</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.026369</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.08594</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.311368</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.114826</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.57064</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.219754</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.09409099999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.713788</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.059381</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.007507</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.054784</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.000329</v>
       </c>
     </row>
     <row r="35">
@@ -2557,40 +2557,40 @@
         <v>0.638646</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.026369</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.08594</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.311368</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.114826</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.57064</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.219754</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.09409099999999999</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>3.713788</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.059381</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.007507</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.054784</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.000329</v>
       </c>
     </row>
     <row r="37">
@@ -3253,40 +3253,40 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.026369</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.08594</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.320081</v>
+        <v>0.008713</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.142955</v>
+        <v>0.028129</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.62919</v>
+        <v>0.05855</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.251039</v>
+        <v>0.031285</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.126912</v>
+        <v>0.032821</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.734564</v>
+        <v>0.020776</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.09213300000000001</v>
+        <v>0.032752</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.013241</v>
+        <v>0.005734</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.07878400000000001</v>
+        <v>0.024</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.002329</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="49">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8885,7 +8885,11 @@
           <t>Reclamation deposits (Note 4)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -15472,7 +15476,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -32003,7 +32011,11 @@
           <t>Reclamation deposit (Note 4)</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -33714,7 +33726,11 @@
           <t>Return of reclamation deposit (Note 4)</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -48734,7 +48750,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -54734,7 +54750,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E469" s="5" t="n">

--- a/output/pdf_financials_xlsx/EGM.xlsx
+++ b/output/pdf_financials_xlsx/EGM.xlsx
@@ -6995,10 +6995,10 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.015976</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -36970,7 +36970,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -39972,7 +39976,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -41255,7 +41263,11 @@
           <t>Non-cash proceeds on disposal of property and equipment $</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/EGM.xlsx
+++ b/output/pdf_financials_xlsx/EGM.xlsx
@@ -6970,7 +6970,7 @@
         <v>0</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002757</v>
       </c>
       <c r="P111" s="3" t="n">
         <v>0</v>
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>0</v>
@@ -7743,10 +7743,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -8338,7 +8338,7 @@
         <v>0</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002757</v>
       </c>
       <c r="P134" s="3" t="n">
         <v>0</v>
@@ -8396,7 +8396,7 @@
         <v>-1.188784</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-3.532825</v>
+        <v>-3.535582</v>
       </c>
       <c r="P135" s="3" t="n">
         <v>-0.568169</v>
@@ -22378,7 +22378,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -24734,7 +24738,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -26318,7 +26326,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -29607,7 +29619,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -30506,7 +30522,11 @@
           <t>Proceeds from share issuances (Note 9)</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -32314,7 +32334,11 @@
           <t>Proceeds from share issuances (Note 10)</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -36162,7 +36186,11 @@
           <t>Deferred tax expense/(recovery)</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -38491,7 +38519,11 @@
           <t>Future income taxes recovery</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E304" s="5" t="n">
         <v>-0.320588</v>
       </c>
@@ -42168,7 +42200,11 @@
           <t>Decrease in long-term debt</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E341" s="5" t="n">
         <v>-0.015</v>
       </c>
